--- a/คำนวน_max_pain_10 (2).xlsx
+++ b/คำนวน_max_pain_10 (2).xlsx
@@ -715,12 +715,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Max Pain Calc'!$A$2:$A$108</f>
+              <f>'Max Pain Calc'!$A$2:$A$134</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Max Pain Calc'!$B$2:$B$108</f>
+              <f>'Max Pain Calc'!$B$2:$B$134</f>
             </numRef>
           </val>
         </ser>
@@ -1001,13 +1001,13 @@
     </row>
     <row r="2" ht="25.5" customHeight="1" s="29">
       <c r="A2" s="2" t="n">
-        <v>3600</v>
+        <v>3750</v>
       </c>
       <c r="B2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="F2" s="26" t="inlineStr">
         <is>
-          <t>AB1 Week 4 - SEP 2026 (U26)</t>
+          <t>MW1 Week 4 - SEP 2026 (U26)</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -1033,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="F3" s="27" t="n">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="F4" s="26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="F5" s="26" t="n">
-        <v>799</v>
+        <v>3432</v>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
@@ -1099,13 +1099,13 @@
     </row>
     <row r="6" ht="25.5" customHeight="1" s="29">
       <c r="A6" s="2" t="n">
-        <v>3950</v>
+        <v>3955</v>
       </c>
       <c r="B6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="F6" s="26" t="n">
-        <v>1015</v>
+        <v>3798</v>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
@@ -1123,35 +1123,35 @@
     </row>
     <row r="7" ht="15" customHeight="1" s="29">
       <c r="A7" s="2" t="n">
-        <v>3975</v>
+        <v>3960</v>
       </c>
       <c r="B7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="29">
       <c r="A8" s="2" t="n">
-        <v>4000</v>
+        <v>3975</v>
       </c>
       <c r="B8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="29">
       <c r="A9" s="2" t="n">
-        <v>4005</v>
+        <v>4000</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="29">
@@ -1162,45 +1162,45 @@
         <v>0</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="29">
       <c r="A11" s="2" t="n">
-        <v>4050</v>
+        <v>4040</v>
       </c>
       <c r="B11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="29">
       <c r="A12" s="2" t="n">
-        <v>4075</v>
+        <v>4045</v>
       </c>
       <c r="B12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="29">
       <c r="A13" s="2" t="n">
-        <v>4100</v>
+        <v>4050</v>
       </c>
       <c r="B13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>311</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="29">
       <c r="A14" s="2" t="n">
-        <v>4120</v>
+        <v>4060</v>
       </c>
       <c r="B14" s="3" t="n">
         <v>0</v>
@@ -1211,73 +1211,73 @@
     </row>
     <row r="15" ht="15" customHeight="1" s="29">
       <c r="A15" s="2" t="n">
-        <v>4125</v>
+        <v>4075</v>
       </c>
       <c r="B15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="29">
       <c r="A16" s="2" t="n">
-        <v>4135</v>
+        <v>4080</v>
       </c>
       <c r="B16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="29">
       <c r="A17" s="2" t="n">
-        <v>4145</v>
+        <v>4085</v>
       </c>
       <c r="B17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="29">
       <c r="A18" s="2" t="n">
-        <v>4150</v>
+        <v>4090</v>
       </c>
       <c r="B18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="29">
       <c r="A19" s="2" t="n">
-        <v>4165</v>
+        <v>4100</v>
       </c>
       <c r="B19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="29">
       <c r="A20" s="2" t="n">
-        <v>4175</v>
+        <v>4105</v>
       </c>
       <c r="B20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>89</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="29">
       <c r="A21" s="2" t="n">
-        <v>4185</v>
+        <v>4115</v>
       </c>
       <c r="B21" s="3" t="n">
         <v>0</v>
@@ -1288,560 +1288,560 @@
     </row>
     <row r="22" ht="15" customHeight="1" s="29">
       <c r="A22" s="2" t="n">
-        <v>4195</v>
+        <v>4120</v>
       </c>
       <c r="B22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="29">
       <c r="A23" s="2" t="n">
-        <v>4200</v>
+        <v>4125</v>
       </c>
       <c r="B23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="29">
       <c r="A24" s="2" t="n">
-        <v>4210</v>
+        <v>4130</v>
       </c>
       <c r="B24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="29">
       <c r="A25" s="2" t="n">
-        <v>4215</v>
+        <v>4135</v>
       </c>
       <c r="B25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="29">
       <c r="A26" s="2" t="n">
-        <v>4225</v>
+        <v>4140</v>
       </c>
       <c r="B26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>95</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="29">
       <c r="A27" s="2" t="n">
-        <v>4235</v>
+        <v>4145</v>
       </c>
       <c r="B27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="29">
       <c r="A28" s="2" t="n">
-        <v>4240</v>
+        <v>4150</v>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>3</v>
+        <v>324</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="29">
       <c r="A29" s="2" t="n">
-        <v>4250</v>
+        <v>4155</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="29">
       <c r="A30" s="2" t="n">
-        <v>4255</v>
+        <v>4160</v>
       </c>
       <c r="B30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="29">
       <c r="A31" s="2" t="n">
-        <v>4260</v>
+        <v>4165</v>
       </c>
       <c r="B31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="29">
       <c r="A32" s="2" t="n">
-        <v>4265</v>
+        <v>4170</v>
       </c>
       <c r="B32" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="29">
       <c r="A33" s="2" t="n">
-        <v>4270</v>
+        <v>4175</v>
       </c>
       <c r="B33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="29">
       <c r="A34" s="2" t="n">
-        <v>4275</v>
+        <v>4180</v>
       </c>
       <c r="B34" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="29">
       <c r="A35" s="2" t="n">
-        <v>4280</v>
+        <v>4185</v>
       </c>
       <c r="B35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="29">
       <c r="A36" s="2" t="n">
-        <v>4285</v>
+        <v>4190</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="29">
       <c r="A37" s="2" t="n">
-        <v>4290</v>
+        <v>4195</v>
       </c>
       <c r="B37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="29">
       <c r="A38" s="2" t="n">
-        <v>4295</v>
+        <v>4200</v>
       </c>
       <c r="B38" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>6</v>
+        <v>561</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="29">
       <c r="A39" s="2" t="n">
-        <v>4300</v>
+        <v>4205</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>24</v>
+        <v>71</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="29">
       <c r="A40" s="2" t="n">
-        <v>4305</v>
+        <v>4210</v>
       </c>
       <c r="B40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="29">
       <c r="A41" s="2" t="n">
-        <v>4310</v>
+        <v>4215</v>
       </c>
       <c r="B41" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="29">
       <c r="A42" s="2" t="n">
-        <v>4315</v>
+        <v>4220</v>
       </c>
       <c r="B42" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="29">
       <c r="A43" s="2" t="n">
-        <v>4320</v>
+        <v>4225</v>
       </c>
       <c r="B43" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>7</v>
+        <v>108</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="29">
       <c r="A44" s="2" t="n">
-        <v>4325</v>
+        <v>4230</v>
       </c>
       <c r="B44" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="29">
       <c r="A45" s="2" t="n">
-        <v>4330</v>
+        <v>4235</v>
       </c>
       <c r="B45" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="29">
       <c r="A46" s="2" t="n">
-        <v>4335</v>
+        <v>4240</v>
       </c>
       <c r="B46" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="29">
       <c r="A47" s="2" t="n">
-        <v>4340</v>
+        <v>4245</v>
       </c>
       <c r="B47" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="29">
       <c r="A48" s="2" t="n">
-        <v>4345</v>
+        <v>4250</v>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>8</v>
+        <v>278</v>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="29">
       <c r="A49" s="2" t="n">
-        <v>4350</v>
+        <v>4255</v>
       </c>
       <c r="B49" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="29">
       <c r="A50" s="2" t="n">
-        <v>4355</v>
+        <v>4260</v>
       </c>
       <c r="B50" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="29">
       <c r="A51" s="2" t="n">
-        <v>4360</v>
+        <v>4265</v>
       </c>
       <c r="B51" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>19</v>
+        <v>61</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="29">
       <c r="A52" s="2" t="n">
-        <v>4365</v>
+        <v>4270</v>
       </c>
       <c r="B52" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>4370</v>
+        <v>4275</v>
       </c>
       <c r="B53" s="3" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>1</v>
+        <v>83</v>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="29">
       <c r="A54" s="2" t="n">
-        <v>4375</v>
+        <v>4280</v>
       </c>
       <c r="B54" s="3" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="29">
       <c r="A55" s="2" t="n">
-        <v>4380</v>
+        <v>4285</v>
       </c>
       <c r="B55" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="29">
       <c r="A56" s="2" t="n">
-        <v>4385</v>
+        <v>4290</v>
       </c>
       <c r="B56" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>4390</v>
+        <v>4295</v>
       </c>
       <c r="B57" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>4395</v>
+        <v>4300</v>
       </c>
       <c r="B58" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>10</v>
+        <v>114</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>4400</v>
+        <v>4305</v>
       </c>
       <c r="B59" s="3" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>4405</v>
+        <v>4310</v>
       </c>
       <c r="B60" s="3" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>4410</v>
+        <v>4315</v>
       </c>
       <c r="B61" s="3" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>4415</v>
+        <v>4320</v>
       </c>
       <c r="B62" s="3" t="n">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>4420</v>
+        <v>4325</v>
       </c>
       <c r="B63" t="n">
-        <v>14</v>
+        <v>120</v>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>533</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>4425</v>
+        <v>4330</v>
       </c>
       <c r="B64" t="n">
-        <v>117</v>
+        <v>26</v>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>4430</v>
+        <v>4335</v>
       </c>
       <c r="B65" t="n">
+        <v>300</v>
+      </c>
+      <c r="C65" t="n">
         <v>21</v>
-      </c>
-      <c r="C65" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>4435</v>
+        <v>4340</v>
       </c>
       <c r="B66" t="n">
-        <v>3</v>
+        <v>252</v>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>4440</v>
+        <v>4345</v>
       </c>
       <c r="B67" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>4445</v>
+        <v>4350</v>
       </c>
       <c r="B68" t="n">
-        <v>25</v>
+        <v>130</v>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>4450</v>
+        <v>4355</v>
       </c>
       <c r="B69" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>4455</v>
+        <v>4360</v>
       </c>
       <c r="B70" t="n">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>4460</v>
+        <v>4365</v>
       </c>
       <c r="B71" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>4465</v>
+        <v>4370</v>
       </c>
       <c r="B72" t="n">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
@@ -1849,32 +1849,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>4470</v>
+        <v>4375</v>
       </c>
       <c r="B73" t="n">
-        <v>23</v>
+        <v>245</v>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>4475</v>
+        <v>4380</v>
       </c>
       <c r="B74" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C74" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>4480</v>
+        <v>4385</v>
       </c>
       <c r="B75" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
@@ -1882,10 +1882,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>4485</v>
+        <v>4390</v>
       </c>
       <c r="B76" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
@@ -1893,54 +1893,54 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>4490</v>
+        <v>4395</v>
       </c>
       <c r="B77" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>4500</v>
+        <v>4400</v>
       </c>
       <c r="B78" t="n">
-        <v>26</v>
+        <v>155</v>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>4510</v>
+        <v>4405</v>
       </c>
       <c r="B79" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>4515</v>
+        <v>4410</v>
       </c>
       <c r="B80" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C80" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>4520</v>
+        <v>4415</v>
       </c>
       <c r="B81" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C81" t="n">
         <v>1</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>4525</v>
+        <v>4420</v>
       </c>
       <c r="B82" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
@@ -1959,21 +1959,21 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>4530</v>
+        <v>4425</v>
       </c>
       <c r="B83" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>4540</v>
+        <v>4430</v>
       </c>
       <c r="B84" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -1981,10 +1981,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>4545</v>
+        <v>4435</v>
       </c>
       <c r="B85" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
@@ -1992,21 +1992,21 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>4550</v>
+        <v>4440</v>
       </c>
       <c r="B86" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>4570</v>
+        <v>4445</v>
       </c>
       <c r="B87" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -2014,21 +2014,21 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>4575</v>
+        <v>4450</v>
       </c>
       <c r="B88" t="n">
-        <v>21</v>
+        <v>137</v>
       </c>
       <c r="C88" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>4580</v>
+        <v>4455</v>
       </c>
       <c r="B89" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
@@ -2036,21 +2036,21 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>4600</v>
+        <v>4460</v>
       </c>
       <c r="B90" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C90" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>4610</v>
+        <v>4465</v>
       </c>
       <c r="B91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
@@ -2058,10 +2058,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>4625</v>
+        <v>4470</v>
       </c>
       <c r="B92" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
@@ -2069,32 +2069,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>4650</v>
+        <v>4475</v>
       </c>
       <c r="B93" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>4675</v>
+        <v>4480</v>
       </c>
       <c r="B94" t="n">
         <v>3</v>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>4685</v>
+        <v>4485</v>
       </c>
       <c r="B95" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
@@ -2102,32 +2102,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>4700</v>
+        <v>4495</v>
       </c>
       <c r="B96" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>4705</v>
+        <v>4500</v>
       </c>
       <c r="B97" t="n">
-        <v>1</v>
+        <v>156</v>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>4725</v>
+        <v>4505</v>
       </c>
       <c r="B98" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -2135,32 +2135,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>4750</v>
+        <v>4510</v>
       </c>
       <c r="B99" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>4775</v>
+        <v>4525</v>
       </c>
       <c r="B100" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C100" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>4800</v>
+        <v>4530</v>
       </c>
       <c r="B101" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
@@ -2168,32 +2168,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>4850</v>
+        <v>4550</v>
       </c>
       <c r="B102" t="n">
-        <v>2</v>
+        <v>215</v>
       </c>
       <c r="C102" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>4900</v>
+        <v>4575</v>
       </c>
       <c r="B103" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C103" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>4925</v>
+        <v>4580</v>
       </c>
       <c r="B104" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
@@ -2201,21 +2201,21 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>4950</v>
+        <v>4600</v>
       </c>
       <c r="B105" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="C105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>4975</v>
+        <v>4605</v>
       </c>
       <c r="B106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
@@ -2223,10 +2223,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>5250</v>
+        <v>4620</v>
       </c>
       <c r="B107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -2234,41 +2234,301 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
+        <v>4625</v>
+      </c>
+      <c r="B108" t="n">
+        <v>79</v>
+      </c>
+      <c r="C108" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>4635</v>
+      </c>
+      <c r="B109" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>4650</v>
+      </c>
+      <c r="B110" t="n">
+        <v>43</v>
+      </c>
+      <c r="C110" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>4675</v>
+      </c>
+      <c r="B111" t="n">
+        <v>16</v>
+      </c>
+      <c r="C111" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>4700</v>
+      </c>
+      <c r="B112" t="n">
+        <v>49</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>4725</v>
+      </c>
+      <c r="B113" t="n">
+        <v>40</v>
+      </c>
+      <c r="C113" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>4750</v>
+      </c>
+      <c r="B114" t="n">
+        <v>18</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>4775</v>
+      </c>
+      <c r="B115" t="n">
+        <v>22</v>
+      </c>
+      <c r="C115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>4800</v>
+      </c>
+      <c r="B116" t="n">
+        <v>43</v>
+      </c>
+      <c r="C116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>4825</v>
+      </c>
+      <c r="B117" t="n">
+        <v>17</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>4850</v>
+      </c>
+      <c r="B118" t="n">
+        <v>67</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>4875</v>
+      </c>
+      <c r="B119" t="n">
+        <v>27</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>4900</v>
+      </c>
+      <c r="B120" t="n">
+        <v>48</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>4925</v>
+      </c>
+      <c r="B121" t="n">
+        <v>53</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>4950</v>
+      </c>
+      <c r="B122" t="n">
+        <v>8</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>4975</v>
+      </c>
+      <c r="B123" t="n">
+        <v>7</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>5000</v>
+      </c>
+      <c r="B124" t="n">
+        <v>96</v>
+      </c>
+      <c r="C124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>5025</v>
+      </c>
+      <c r="B125" t="n">
+        <v>11</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>5050</v>
+      </c>
+      <c r="B126" t="n">
+        <v>6</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>5075</v>
+      </c>
+      <c r="B127" t="n">
+        <v>4</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>5100</v>
+      </c>
+      <c r="B128" t="n">
+        <v>7</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>5125</v>
+      </c>
+      <c r="B129" t="n">
+        <v>5</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>5150</v>
+      </c>
+      <c r="B130" t="n">
+        <v>12</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>5200</v>
+      </c>
+      <c r="B131" t="n">
+        <v>16</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>5250</v>
+      </c>
+      <c r="B132" t="n">
+        <v>11</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>5300</v>
+      </c>
+      <c r="B133" t="n">
+        <v>4</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
         <v>5400</v>
       </c>
-      <c r="B108" t="n">
-        <v>1</v>
-      </c>
-      <c r="C108" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
+      <c r="B134" t="n">
+        <v>17</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="135"/>
     <row r="136"/>
     <row r="137"/>
@@ -2460,7 +2720,7 @@
         </is>
       </c>
       <c r="F4" s="30" t="n">
-        <v>4390.7</v>
+        <v>4321.2</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="29">
@@ -5556,7 +5816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5691,7 +5951,95 @@
         </is>
       </c>
       <c r="K3" s="43" t="n">
-        <v>46286.9068986949</v>
+        <v>46286.90689869213</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="35" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>E21 Week 4 - SEP 2026 (U26)</t>
+        </is>
+      </c>
+      <c r="C4" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="42" t="n">
+        <v>4318.4</v>
+      </c>
+      <c r="E4" s="36" t="n">
+        <v>4355</v>
+      </c>
+      <c r="F4" s="38" t="n">
+        <v>0.008475361244905605</v>
+      </c>
+      <c r="G4" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" s="39" t="n">
+        <v>0.7977815699658704</v>
+      </c>
+      <c r="I4" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>PRELIMINARY</t>
+        </is>
+      </c>
+      <c r="K4" s="43" t="n">
+        <v>46289.80939699074</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>DEC 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="35" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MW1 Week 4 - SEP 2026 (U26)</t>
+        </is>
+      </c>
+      <c r="C5" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="42" t="n">
+        <v>4321.2</v>
+      </c>
+      <c r="E5" s="36" t="n">
+        <v>4330</v>
+      </c>
+      <c r="F5" s="38" t="n">
+        <v>0.002036471350550815</v>
+      </c>
+      <c r="G5" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" s="39" t="n">
+        <v>1.106643356643357</v>
+      </c>
+      <c r="I5" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>PRELIMINARY</t>
+        </is>
+      </c>
+      <c r="K5" s="43" t="n">
+        <v>46292.67259951946</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>DEC 26</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/คำนวน_max_pain_10 (2).xlsx
+++ b/คำนวน_max_pain_10 (2).xlsx
@@ -6034,7 +6034,7 @@
         </is>
       </c>
       <c r="K5" s="43" t="n">
-        <v>46292.67259951946</v>
+        <v>46292.69501100385</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>

--- a/คำนวน_max_pain_10 (2).xlsx
+++ b/คำนวน_max_pain_10 (2).xlsx
@@ -715,12 +715,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Max Pain Calc'!$A$2:$A$134</f>
+              <f>'Max Pain Calc'!$A$2:$A$144</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Max Pain Calc'!$B$2:$B$134</f>
+              <f>'Max Pain Calc'!$B$2:$B$144</f>
             </numRef>
           </val>
         </ser>
@@ -1001,13 +1001,13 @@
     </row>
     <row r="2" ht="25.5" customHeight="1" s="29">
       <c r="A2" s="2" t="n">
-        <v>3750</v>
+        <v>3500</v>
       </c>
       <c r="B2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="F2" s="26" t="inlineStr">
         <is>
-          <t>MW1 Week 4 - SEP 2026 (U26)</t>
+          <t>E21 Week 1 - OCT 2026 (V26)</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -1027,13 +1027,13 @@
     </row>
     <row r="3" ht="25.5" customHeight="1" s="29">
       <c r="A3" s="2" t="n">
-        <v>3800</v>
+        <v>3600</v>
       </c>
       <c r="B3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="F3" s="27" t="n">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
@@ -1051,13 +1051,13 @@
     </row>
     <row r="4" ht="25.5" customHeight="1" s="29">
       <c r="A4" s="2" t="n">
-        <v>3900</v>
+        <v>3700</v>
       </c>
       <c r="B4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="F4" s="26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
@@ -1075,13 +1075,13 @@
     </row>
     <row r="5" ht="25.5" customHeight="1" s="29">
       <c r="A5" s="2" t="n">
-        <v>3925</v>
+        <v>3750</v>
       </c>
       <c r="B5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="F5" s="26" t="n">
-        <v>3432</v>
+        <v>4959</v>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
@@ -1099,13 +1099,13 @@
     </row>
     <row r="6" ht="25.5" customHeight="1" s="29">
       <c r="A6" s="2" t="n">
-        <v>3955</v>
+        <v>3795</v>
       </c>
       <c r="B6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="F6" s="26" t="n">
-        <v>3798</v>
+        <v>6211</v>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
@@ -1123,51 +1123,51 @@
     </row>
     <row r="7" ht="15" customHeight="1" s="29">
       <c r="A7" s="2" t="n">
-        <v>3960</v>
+        <v>3800</v>
       </c>
       <c r="B7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>5</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="29">
       <c r="A8" s="2" t="n">
-        <v>3975</v>
+        <v>3815</v>
       </c>
       <c r="B8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="29">
       <c r="A9" s="2" t="n">
-        <v>4000</v>
+        <v>3835</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>135</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="29">
       <c r="A10" s="2" t="n">
-        <v>4025</v>
+        <v>3860</v>
       </c>
       <c r="B10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="29">
       <c r="A11" s="2" t="n">
-        <v>4040</v>
+        <v>3870</v>
       </c>
       <c r="B11" s="3" t="n">
         <v>0</v>
@@ -1178,692 +1178,692 @@
     </row>
     <row r="12" ht="15" customHeight="1" s="29">
       <c r="A12" s="2" t="n">
-        <v>4045</v>
+        <v>3875</v>
       </c>
       <c r="B12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="29">
       <c r="A13" s="2" t="n">
-        <v>4050</v>
+        <v>3890</v>
       </c>
       <c r="B13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="29">
       <c r="A14" s="2" t="n">
-        <v>4060</v>
+        <v>3895</v>
       </c>
       <c r="B14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="29">
       <c r="A15" s="2" t="n">
-        <v>4075</v>
+        <v>3900</v>
       </c>
       <c r="B15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>55</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="29">
       <c r="A16" s="2" t="n">
-        <v>4080</v>
+        <v>3910</v>
       </c>
       <c r="B16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>61</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="29">
       <c r="A17" s="2" t="n">
-        <v>4085</v>
+        <v>3920</v>
       </c>
       <c r="B17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="29">
       <c r="A18" s="2" t="n">
-        <v>4090</v>
+        <v>3925</v>
       </c>
       <c r="B18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1</v>
+        <v>162</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="29">
       <c r="A19" s="2" t="n">
-        <v>4100</v>
+        <v>3930</v>
       </c>
       <c r="B19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>136</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="29">
       <c r="A20" s="2" t="n">
-        <v>4105</v>
+        <v>3940</v>
       </c>
       <c r="B20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="29">
       <c r="A21" s="2" t="n">
-        <v>4115</v>
+        <v>3950</v>
       </c>
       <c r="B21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="29">
       <c r="A22" s="2" t="n">
-        <v>4120</v>
+        <v>3955</v>
       </c>
       <c r="B22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="29">
       <c r="A23" s="2" t="n">
-        <v>4125</v>
+        <v>3960</v>
       </c>
       <c r="B23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="29">
       <c r="A24" s="2" t="n">
-        <v>4130</v>
+        <v>3965</v>
       </c>
       <c r="B24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="29">
       <c r="A25" s="2" t="n">
-        <v>4135</v>
+        <v>3970</v>
       </c>
       <c r="B25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="29">
       <c r="A26" s="2" t="n">
-        <v>4140</v>
+        <v>3975</v>
       </c>
       <c r="B26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="29">
       <c r="A27" s="2" t="n">
-        <v>4145</v>
+        <v>3980</v>
       </c>
       <c r="B27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>12</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="29">
       <c r="A28" s="2" t="n">
-        <v>4150</v>
+        <v>3985</v>
       </c>
       <c r="B28" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>324</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="29">
       <c r="A29" s="2" t="n">
-        <v>4155</v>
+        <v>3990</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="29">
       <c r="A30" s="2" t="n">
-        <v>4160</v>
+        <v>3995</v>
       </c>
       <c r="B30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="29">
       <c r="A31" s="2" t="n">
-        <v>4165</v>
+        <v>4000</v>
       </c>
       <c r="B31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>2</v>
+        <v>349</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="29">
       <c r="A32" s="2" t="n">
-        <v>4170</v>
+        <v>4005</v>
       </c>
       <c r="B32" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="29">
       <c r="A33" s="2" t="n">
-        <v>4175</v>
+        <v>4010</v>
       </c>
       <c r="B33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="29">
       <c r="A34" s="2" t="n">
-        <v>4180</v>
+        <v>4015</v>
       </c>
       <c r="B34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="29">
       <c r="A35" s="2" t="n">
-        <v>4185</v>
+        <v>4020</v>
       </c>
       <c r="B35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="29">
       <c r="A36" s="2" t="n">
-        <v>4190</v>
+        <v>4025</v>
       </c>
       <c r="B36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>11</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="29">
       <c r="A37" s="2" t="n">
-        <v>4195</v>
+        <v>4030</v>
       </c>
       <c r="B37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="29">
       <c r="A38" s="2" t="n">
-        <v>4200</v>
+        <v>4035</v>
       </c>
       <c r="B38" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>561</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="29">
       <c r="A39" s="2" t="n">
-        <v>4205</v>
+        <v>4040</v>
       </c>
       <c r="B39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="29">
       <c r="A40" s="2" t="n">
-        <v>4210</v>
+        <v>4045</v>
       </c>
       <c r="B40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="29">
       <c r="A41" s="2" t="n">
-        <v>4215</v>
+        <v>4050</v>
       </c>
       <c r="B41" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>8</v>
+        <v>147</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="29">
       <c r="A42" s="2" t="n">
-        <v>4220</v>
+        <v>4055</v>
       </c>
       <c r="B42" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="29">
       <c r="A43" s="2" t="n">
-        <v>4225</v>
+        <v>4060</v>
       </c>
       <c r="B43" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>108</v>
+        <v>24</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="29">
       <c r="A44" s="2" t="n">
-        <v>4230</v>
+        <v>4065</v>
       </c>
       <c r="B44" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="29">
       <c r="A45" s="2" t="n">
-        <v>4235</v>
+        <v>4070</v>
       </c>
       <c r="B45" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>37</v>
+        <v>159</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="29">
       <c r="A46" s="2" t="n">
-        <v>4240</v>
+        <v>4075</v>
       </c>
       <c r="B46" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>24</v>
+        <v>281</v>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="29">
       <c r="A47" s="2" t="n">
-        <v>4245</v>
+        <v>4080</v>
       </c>
       <c r="B47" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="29">
       <c r="A48" s="2" t="n">
-        <v>4250</v>
+        <v>4085</v>
       </c>
       <c r="B48" s="3" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>278</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="29">
       <c r="A49" s="2" t="n">
-        <v>4255</v>
+        <v>4090</v>
       </c>
       <c r="B49" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="29">
       <c r="A50" s="2" t="n">
-        <v>4260</v>
+        <v>4095</v>
       </c>
       <c r="B50" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="29">
       <c r="A51" s="2" t="n">
-        <v>4265</v>
+        <v>4100</v>
       </c>
       <c r="B51" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>61</v>
+        <v>540</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="29">
       <c r="A52" s="2" t="n">
-        <v>4270</v>
+        <v>4105</v>
       </c>
       <c r="B52" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>4275</v>
+        <v>4110</v>
       </c>
       <c r="B53" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>83</v>
+        <v>26</v>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="29">
       <c r="A54" s="2" t="n">
-        <v>4280</v>
+        <v>4115</v>
       </c>
       <c r="B54" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>55</v>
+        <v>14</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="29">
       <c r="A55" s="2" t="n">
-        <v>4285</v>
+        <v>4120</v>
       </c>
       <c r="B55" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="29">
       <c r="A56" s="2" t="n">
-        <v>4290</v>
+        <v>4125</v>
       </c>
       <c r="B56" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>7</v>
+        <v>128</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>4295</v>
+        <v>4130</v>
       </c>
       <c r="B57" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>14</v>
+        <v>102</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>4300</v>
+        <v>4135</v>
       </c>
       <c r="B58" s="3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>114</v>
+        <v>33</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>4305</v>
+        <v>4140</v>
       </c>
       <c r="B59" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>14</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>4310</v>
+        <v>4145</v>
       </c>
       <c r="B60" s="3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>4315</v>
+        <v>4150</v>
       </c>
       <c r="B61" s="3" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>18</v>
+        <v>385</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>4320</v>
+        <v>4155</v>
       </c>
       <c r="B62" s="3" t="n">
-        <v>82</v>
+        <v>4</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>107</v>
+        <v>18</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>4325</v>
+        <v>4160</v>
       </c>
       <c r="B63" t="n">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="C63" t="n">
-        <v>533</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>4330</v>
+        <v>4165</v>
       </c>
       <c r="B64" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="C64" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>4335</v>
+        <v>4170</v>
       </c>
       <c r="B65" t="n">
-        <v>300</v>
+        <v>8</v>
       </c>
       <c r="C65" t="n">
-        <v>21</v>
+        <v>56</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>4340</v>
+        <v>4175</v>
       </c>
       <c r="B66" t="n">
-        <v>252</v>
+        <v>10</v>
       </c>
       <c r="C66" t="n">
-        <v>13</v>
+        <v>105</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>4345</v>
+        <v>4180</v>
       </c>
       <c r="B67" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="C67" t="n">
-        <v>29</v>
+        <v>56</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>4350</v>
+        <v>4185</v>
       </c>
       <c r="B68" t="n">
-        <v>130</v>
+        <v>8</v>
       </c>
       <c r="C68" t="n">
-        <v>46</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>4355</v>
+        <v>4190</v>
       </c>
       <c r="B69" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>4360</v>
+        <v>4195</v>
       </c>
       <c r="B70" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="C70" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>4365</v>
+        <v>4200</v>
       </c>
       <c r="B71" t="n">
-        <v>17</v>
+        <v>115</v>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>451</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>4370</v>
+        <v>4205</v>
       </c>
       <c r="B72" t="n">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>4375</v>
+        <v>4210</v>
       </c>
       <c r="B73" t="n">
-        <v>245</v>
+        <v>26</v>
       </c>
       <c r="C73" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>4380</v>
+        <v>4215</v>
       </c>
       <c r="B74" t="n">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
@@ -1871,109 +1871,109 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>4385</v>
+        <v>4220</v>
       </c>
       <c r="B75" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>4390</v>
+        <v>4225</v>
       </c>
       <c r="B76" t="n">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="C76" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>4395</v>
+        <v>4230</v>
       </c>
       <c r="B77" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C77" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>4400</v>
+        <v>4235</v>
       </c>
       <c r="B78" t="n">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C78" t="n">
-        <v>62</v>
+        <v>10</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>4405</v>
+        <v>4240</v>
       </c>
       <c r="B79" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C79" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>4410</v>
+        <v>4245</v>
       </c>
       <c r="B80" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C80" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>4415</v>
+        <v>4250</v>
       </c>
       <c r="B81" t="n">
-        <v>26</v>
+        <v>181</v>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>413</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>4420</v>
+        <v>4255</v>
       </c>
       <c r="B82" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>4425</v>
+        <v>4260</v>
       </c>
       <c r="B83" t="n">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="C83" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>4430</v>
+        <v>4265</v>
       </c>
       <c r="B84" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -1981,54 +1981,54 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>4435</v>
+        <v>4270</v>
       </c>
       <c r="B85" t="n">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>4440</v>
+        <v>4275</v>
       </c>
       <c r="B86" t="n">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>4445</v>
+        <v>4280</v>
       </c>
       <c r="B87" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>4450</v>
+        <v>4285</v>
       </c>
       <c r="B88" t="n">
-        <v>137</v>
+        <v>30</v>
       </c>
       <c r="C88" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>4455</v>
+        <v>4290</v>
       </c>
       <c r="B89" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>4460</v>
+        <v>4295</v>
       </c>
       <c r="B90" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
@@ -2047,21 +2047,21 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>4465</v>
+        <v>4300</v>
       </c>
       <c r="B91" t="n">
-        <v>3</v>
+        <v>303</v>
       </c>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>435</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>4470</v>
+        <v>4305</v>
       </c>
       <c r="B92" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
@@ -2069,21 +2069,21 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>4475</v>
+        <v>4310</v>
       </c>
       <c r="B93" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="C93" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>4480</v>
+        <v>4315</v>
       </c>
       <c r="B94" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
@@ -2091,43 +2091,43 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>4485</v>
+        <v>4320</v>
       </c>
       <c r="B95" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>4495</v>
+        <v>4325</v>
       </c>
       <c r="B96" t="n">
-        <v>14</v>
+        <v>206</v>
       </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>185</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>4500</v>
+        <v>4330</v>
       </c>
       <c r="B97" t="n">
-        <v>156</v>
+        <v>44</v>
       </c>
       <c r="C97" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>4505</v>
+        <v>4335</v>
       </c>
       <c r="B98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -2135,65 +2135,65 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>4510</v>
+        <v>4340</v>
       </c>
       <c r="B99" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>4525</v>
+        <v>4345</v>
       </c>
       <c r="B100" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C100" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>4530</v>
+        <v>4350</v>
       </c>
       <c r="B101" t="n">
-        <v>2</v>
+        <v>222</v>
       </c>
       <c r="C101" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>4550</v>
+        <v>4355</v>
       </c>
       <c r="B102" t="n">
-        <v>215</v>
+        <v>5</v>
       </c>
       <c r="C102" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>4575</v>
+        <v>4360</v>
       </c>
       <c r="B103" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="C103" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>4580</v>
+        <v>4365</v>
       </c>
       <c r="B104" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
@@ -2201,32 +2201,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>4600</v>
+        <v>4370</v>
       </c>
       <c r="B105" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="C105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>4605</v>
+        <v>4375</v>
       </c>
       <c r="B106" t="n">
-        <v>1</v>
+        <v>450</v>
       </c>
       <c r="C106" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>4620</v>
+        <v>4380</v>
       </c>
       <c r="B107" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -2234,21 +2234,21 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>4625</v>
+        <v>4385</v>
       </c>
       <c r="B108" t="n">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="C108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>4635</v>
+        <v>4390</v>
       </c>
       <c r="B109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -2256,32 +2256,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>4650</v>
+        <v>4395</v>
       </c>
       <c r="B110" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="C110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>4675</v>
+        <v>4400</v>
       </c>
       <c r="B111" t="n">
-        <v>16</v>
+        <v>569</v>
       </c>
       <c r="C111" t="n">
-        <v>2</v>
+        <v>170</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>4700</v>
+        <v>4405</v>
       </c>
       <c r="B112" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
@@ -2289,21 +2289,21 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>4725</v>
+        <v>4410</v>
       </c>
       <c r="B113" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="C113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>4750</v>
+        <v>4415</v>
       </c>
       <c r="B114" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
@@ -2311,10 +2311,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>4775</v>
+        <v>4420</v>
       </c>
       <c r="B115" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
@@ -2322,32 +2322,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>4800</v>
+        <v>4425</v>
       </c>
       <c r="B116" t="n">
-        <v>43</v>
+        <v>249</v>
       </c>
       <c r="C116" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>4825</v>
+        <v>4450</v>
       </c>
       <c r="B117" t="n">
-        <v>17</v>
+        <v>150</v>
       </c>
       <c r="C117" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>4850</v>
+        <v>4455</v>
       </c>
       <c r="B118" t="n">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
@@ -2355,10 +2355,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>4875</v>
+        <v>4470</v>
       </c>
       <c r="B119" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
@@ -2366,32 +2366,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>4900</v>
+        <v>4475</v>
       </c>
       <c r="B120" t="n">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="C120" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>4925</v>
+        <v>4500</v>
       </c>
       <c r="B121" t="n">
-        <v>53</v>
+        <v>326</v>
       </c>
       <c r="C121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>4950</v>
+        <v>4510</v>
       </c>
       <c r="B122" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
@@ -2399,21 +2399,21 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>4975</v>
+        <v>4525</v>
       </c>
       <c r="B123" t="n">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="C123" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>5000</v>
+        <v>4540</v>
       </c>
       <c r="B124" t="n">
-        <v>96</v>
+        <v>1</v>
       </c>
       <c r="C124" t="n">
         <v>0</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>5025</v>
+        <v>4550</v>
       </c>
       <c r="B125" t="n">
-        <v>11</v>
+        <v>371</v>
       </c>
       <c r="C125" t="n">
         <v>0</v>
@@ -2432,10 +2432,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>5050</v>
+        <v>4560</v>
       </c>
       <c r="B126" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
@@ -2443,21 +2443,21 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>5075</v>
+        <v>4575</v>
       </c>
       <c r="B127" t="n">
+        <v>31</v>
+      </c>
+      <c r="C127" t="n">
         <v>4</v>
-      </c>
-      <c r="C127" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>5100</v>
+        <v>4590</v>
       </c>
       <c r="B128" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>5125</v>
+        <v>4600</v>
       </c>
       <c r="B129" t="n">
-        <v>5</v>
+        <v>319</v>
       </c>
       <c r="C129" t="n">
         <v>0</v>
@@ -2476,21 +2476,21 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>5150</v>
+        <v>4625</v>
       </c>
       <c r="B130" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>5200</v>
+        <v>4650</v>
       </c>
       <c r="B131" t="n">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
@@ -2498,10 +2498,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>5250</v>
+        <v>4675</v>
       </c>
       <c r="B132" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
@@ -2509,10 +2509,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>5300</v>
+        <v>4700</v>
       </c>
       <c r="B133" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
@@ -2520,25 +2520,125 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>5400</v>
+        <v>4725</v>
       </c>
       <c r="B134" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>4750</v>
+      </c>
+      <c r="B135" t="n">
+        <v>104</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>4775</v>
+      </c>
+      <c r="B136" t="n">
+        <v>28</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>4800</v>
+      </c>
+      <c r="B137" t="n">
+        <v>57</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>4850</v>
+      </c>
+      <c r="B138" t="n">
+        <v>101</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>4875</v>
+      </c>
+      <c r="B139" t="n">
+        <v>27</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>4900</v>
+      </c>
+      <c r="B140" t="n">
+        <v>8</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>5000</v>
+      </c>
+      <c r="B141" t="n">
+        <v>5</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>5100</v>
+      </c>
+      <c r="B142" t="n">
+        <v>6</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>5200</v>
+      </c>
+      <c r="B143" t="n">
+        <v>15</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>10000</v>
+      </c>
+      <c r="B144" t="n">
+        <v>0</v>
+      </c>
+      <c r="C144" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="145"/>
     <row r="146"/>
     <row r="147"/>
@@ -2720,7 +2820,7 @@
         </is>
       </c>
       <c r="F4" s="30" t="n">
-        <v>4321.2</v>
+        <v>4186.7</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="29">
@@ -5816,7 +5916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6034,9 +6134,141 @@
         </is>
       </c>
       <c r="K5" s="43" t="n">
-        <v>46292.69501100385</v>
+        <v>46292.69501100694</v>
       </c>
       <c r="L5" t="inlineStr">
+        <is>
+          <t>DEC 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="35" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BB1 Week 1 - OCT 2026 (V26)</t>
+        </is>
+      </c>
+      <c r="C6" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="42" t="n">
+        <v>4179.7</v>
+      </c>
+      <c r="E6" s="36" t="n">
+        <v>4250</v>
+      </c>
+      <c r="F6" s="38" t="n">
+        <v>0.01681938895136019</v>
+      </c>
+      <c r="G6" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" s="39" t="n">
+        <v>1.168972746331237</v>
+      </c>
+      <c r="I6" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>FINAL</t>
+        </is>
+      </c>
+      <c r="K6" s="43" t="n">
+        <v>46296.37572123842</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>DEC 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="35" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BB1 Week 1 - OCT 2026 (V26)</t>
+        </is>
+      </c>
+      <c r="C7" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="42" t="n">
+        <v>4186.7</v>
+      </c>
+      <c r="E7" s="36" t="n">
+        <v>4230</v>
+      </c>
+      <c r="F7" s="38" t="n">
+        <v>0.01034227434494953</v>
+      </c>
+      <c r="G7" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" s="39" t="n">
+        <v>1.115485564304462</v>
+      </c>
+      <c r="I7" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>PRELIMINARY</t>
+        </is>
+      </c>
+      <c r="K7" s="43" t="n">
+        <v>46296.61733435185</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>DEC 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="35" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>E21 Week 1 - OCT 2026 (V26)</t>
+        </is>
+      </c>
+      <c r="C8" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="42" t="n">
+        <v>4186.7</v>
+      </c>
+      <c r="E8" s="36" t="n">
+        <v>4300</v>
+      </c>
+      <c r="F8" s="38" t="n">
+        <v>0.02706188644994869</v>
+      </c>
+      <c r="G8" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" s="39" t="n">
+        <v>1.25247025610002</v>
+      </c>
+      <c r="I8" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>FINAL</t>
+        </is>
+      </c>
+      <c r="K8" s="43" t="n">
+        <v>46297.40944206915</v>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>DEC 26</t>
         </is>

--- a/คำนวน_max_pain_10 (2).xlsx
+++ b/คำนวน_max_pain_10 (2).xlsx
@@ -6034,7 +6034,7 @@
         </is>
       </c>
       <c r="K5" s="43" t="n">
-        <v>46292.69501100385</v>
+        <v>46292.78674093509</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>

--- a/คำนวน_max_pain_10 (2).xlsx
+++ b/คำนวน_max_pain_10 (2).xlsx
@@ -715,12 +715,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Max Pain Calc'!$A$2:$A$144</f>
+              <f>'Max Pain Calc'!$A$2:$A$102</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Max Pain Calc'!$B$2:$B$144</f>
+              <f>'Max Pain Calc'!$B$2:$B$102</f>
             </numRef>
           </val>
         </ser>
@@ -1001,13 +1001,13 @@
     </row>
     <row r="2" ht="25.5" customHeight="1" s="29">
       <c r="A2" s="2" t="n">
-        <v>3500</v>
+        <v>3750</v>
       </c>
       <c r="B2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="F2" s="26" t="inlineStr">
         <is>
-          <t>E21 Week 1 - OCT 2026 (V26)</t>
+          <t>AB1 Week 1 - OCT 2026 (V26)</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -1027,13 +1027,13 @@
     </row>
     <row r="3" ht="25.5" customHeight="1" s="29">
       <c r="A3" s="2" t="n">
-        <v>3600</v>
+        <v>3850</v>
       </c>
       <c r="B3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="F3" s="27" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
@@ -1051,13 +1051,13 @@
     </row>
     <row r="4" ht="25.5" customHeight="1" s="29">
       <c r="A4" s="2" t="n">
-        <v>3700</v>
+        <v>3875</v>
       </c>
       <c r="B4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="F4" s="26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
@@ -1075,13 +1075,13 @@
     </row>
     <row r="5" ht="25.5" customHeight="1" s="29">
       <c r="A5" s="2" t="n">
-        <v>3750</v>
+        <v>3895</v>
       </c>
       <c r="B5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="F5" s="26" t="n">
-        <v>4959</v>
+        <v>1749</v>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6" ht="25.5" customHeight="1" s="29">
       <c r="A6" s="2" t="n">
-        <v>3795</v>
+        <v>3900</v>
       </c>
       <c r="B6" s="3" t="n">
         <v>0</v>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="F6" s="26" t="n">
-        <v>6211</v>
+        <v>1454</v>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
@@ -1123,747 +1123,747 @@
     </row>
     <row r="7" ht="15" customHeight="1" s="29">
       <c r="A7" s="2" t="n">
-        <v>3800</v>
+        <v>3915</v>
       </c>
       <c r="B7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>71</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="29">
       <c r="A8" s="2" t="n">
-        <v>3815</v>
+        <v>3950</v>
       </c>
       <c r="B8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="29">
       <c r="A9" s="2" t="n">
-        <v>3835</v>
+        <v>3960</v>
       </c>
       <c r="B9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="29">
       <c r="A10" s="2" t="n">
-        <v>3860</v>
+        <v>3975</v>
       </c>
       <c r="B10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="29">
       <c r="A11" s="2" t="n">
-        <v>3870</v>
+        <v>3980</v>
       </c>
       <c r="B11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="29">
       <c r="A12" s="2" t="n">
-        <v>3875</v>
+        <v>3995</v>
       </c>
       <c r="B12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="29">
       <c r="A13" s="2" t="n">
-        <v>3890</v>
+        <v>4000</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="29">
       <c r="A14" s="2" t="n">
-        <v>3895</v>
+        <v>4025</v>
       </c>
       <c r="B14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="29">
       <c r="A15" s="2" t="n">
-        <v>3900</v>
+        <v>4035</v>
       </c>
       <c r="B15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>156</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="29">
       <c r="A16" s="2" t="n">
-        <v>3910</v>
+        <v>4045</v>
       </c>
       <c r="B16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="29">
       <c r="A17" s="2" t="n">
-        <v>3920</v>
+        <v>4050</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="29">
       <c r="A18" s="2" t="n">
-        <v>3925</v>
+        <v>4055</v>
       </c>
       <c r="B18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>162</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="29">
       <c r="A19" s="2" t="n">
-        <v>3930</v>
+        <v>4060</v>
       </c>
       <c r="B19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="29">
       <c r="A20" s="2" t="n">
-        <v>3940</v>
+        <v>4065</v>
       </c>
       <c r="B20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="29">
       <c r="A21" s="2" t="n">
-        <v>3950</v>
+        <v>4070</v>
       </c>
       <c r="B21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="29">
       <c r="A22" s="2" t="n">
-        <v>3955</v>
+        <v>4075</v>
       </c>
       <c r="B22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="29">
       <c r="A23" s="2" t="n">
-        <v>3960</v>
+        <v>4080</v>
       </c>
       <c r="B23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="29">
       <c r="A24" s="2" t="n">
-        <v>3965</v>
+        <v>4085</v>
       </c>
       <c r="B24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="29">
       <c r="A25" s="2" t="n">
-        <v>3970</v>
+        <v>4090</v>
       </c>
       <c r="B25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="29">
       <c r="A26" s="2" t="n">
-        <v>3975</v>
+        <v>4100</v>
       </c>
       <c r="B26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>39</v>
+        <v>259</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="29">
       <c r="A27" s="2" t="n">
-        <v>3980</v>
+        <v>4105</v>
       </c>
       <c r="B27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>129</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="29">
       <c r="A28" s="2" t="n">
-        <v>3985</v>
+        <v>4110</v>
       </c>
       <c r="B28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>52</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="29">
       <c r="A29" s="2" t="n">
-        <v>3990</v>
+        <v>4115</v>
       </c>
       <c r="B29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="29">
       <c r="A30" s="2" t="n">
-        <v>3995</v>
+        <v>4120</v>
       </c>
       <c r="B30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="29">
       <c r="A31" s="2" t="n">
-        <v>4000</v>
+        <v>4125</v>
       </c>
       <c r="B31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>349</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="29">
       <c r="A32" s="2" t="n">
-        <v>4005</v>
+        <v>4135</v>
       </c>
       <c r="B32" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="29">
       <c r="A33" s="2" t="n">
-        <v>4010</v>
+        <v>4140</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="29">
       <c r="A34" s="2" t="n">
-        <v>4015</v>
+        <v>4145</v>
       </c>
       <c r="B34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="29">
       <c r="A35" s="2" t="n">
-        <v>4020</v>
+        <v>4150</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="29">
       <c r="A36" s="2" t="n">
-        <v>4025</v>
+        <v>4155</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="29">
       <c r="A37" s="2" t="n">
-        <v>4030</v>
+        <v>4160</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="29">
       <c r="A38" s="2" t="n">
-        <v>4035</v>
+        <v>4165</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="29">
       <c r="A39" s="2" t="n">
-        <v>4040</v>
+        <v>4170</v>
       </c>
       <c r="B39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>88</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="29">
       <c r="A40" s="2" t="n">
-        <v>4045</v>
+        <v>4175</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>13</v>
+        <v>209</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="29">
       <c r="A41" s="2" t="n">
-        <v>4050</v>
+        <v>4180</v>
       </c>
       <c r="B41" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>147</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="29">
       <c r="A42" s="2" t="n">
-        <v>4055</v>
+        <v>4185</v>
       </c>
       <c r="B42" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="29">
       <c r="A43" s="2" t="n">
-        <v>4060</v>
+        <v>4190</v>
       </c>
       <c r="B43" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="29">
       <c r="A44" s="2" t="n">
-        <v>4065</v>
+        <v>4195</v>
       </c>
       <c r="B44" s="3" t="n">
-        <v>2</v>
+        <v>111</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="29">
       <c r="A45" s="2" t="n">
-        <v>4070</v>
+        <v>4200</v>
       </c>
       <c r="B45" s="3" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>159</v>
+        <v>62</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="29">
       <c r="A46" s="2" t="n">
-        <v>4075</v>
+        <v>4205</v>
       </c>
       <c r="B46" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>281</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="29">
       <c r="A47" s="2" t="n">
-        <v>4080</v>
+        <v>4210</v>
       </c>
       <c r="B47" s="3" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="29">
       <c r="A48" s="2" t="n">
-        <v>4085</v>
+        <v>4215</v>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="29">
       <c r="A49" s="2" t="n">
-        <v>4090</v>
+        <v>4220</v>
       </c>
       <c r="B49" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="29">
       <c r="A50" s="2" t="n">
-        <v>4095</v>
+        <v>4225</v>
       </c>
       <c r="B50" s="3" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>12</v>
+        <v>63</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="29">
       <c r="A51" s="2" t="n">
-        <v>4100</v>
+        <v>4230</v>
       </c>
       <c r="B51" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>540</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="29">
       <c r="A52" s="2" t="n">
-        <v>4105</v>
+        <v>4235</v>
       </c>
       <c r="B52" s="3" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>4110</v>
+        <v>4240</v>
       </c>
       <c r="B53" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="29">
       <c r="A54" s="2" t="n">
-        <v>4115</v>
+        <v>4245</v>
       </c>
       <c r="B54" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="29">
       <c r="A55" s="2" t="n">
-        <v>4120</v>
+        <v>4250</v>
       </c>
       <c r="B55" s="3" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="29">
       <c r="A56" s="2" t="n">
-        <v>4125</v>
+        <v>4255</v>
       </c>
       <c r="B56" s="3" t="n">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>4130</v>
+        <v>4260</v>
       </c>
       <c r="B57" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C57" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="C57" s="3" t="n">
-        <v>102</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>4135</v>
+        <v>4265</v>
       </c>
       <c r="B58" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>4140</v>
+        <v>4270</v>
       </c>
       <c r="B59" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>4145</v>
+        <v>4275</v>
       </c>
       <c r="B60" s="3" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>47</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>4150</v>
+        <v>4280</v>
       </c>
       <c r="B61" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>4155</v>
+        <v>4285</v>
       </c>
       <c r="B62" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>4160</v>
+        <v>4300</v>
       </c>
       <c r="B63" t="n">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="C63" t="n">
-        <v>19</v>
+        <v>57</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>4165</v>
+        <v>4305</v>
       </c>
       <c r="B64" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>4170</v>
+        <v>4310</v>
       </c>
       <c r="B65" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C65" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>4175</v>
+        <v>4315</v>
       </c>
       <c r="B66" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C66" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>4180</v>
+        <v>4320</v>
       </c>
       <c r="B67" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="C67" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>4185</v>
+        <v>4325</v>
       </c>
       <c r="B68" t="n">
-        <v>8</v>
+        <v>185</v>
       </c>
       <c r="C68" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>4190</v>
+        <v>4330</v>
       </c>
       <c r="B69" t="n">
         <v>0</v>
       </c>
       <c r="C69" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>4195</v>
+        <v>4340</v>
       </c>
       <c r="B70" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C70" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>4200</v>
+        <v>4345</v>
       </c>
       <c r="B71" t="n">
-        <v>115</v>
+        <v>2</v>
       </c>
       <c r="C71" t="n">
-        <v>451</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>4205</v>
+        <v>4350</v>
       </c>
       <c r="B72" t="n">
-        <v>19</v>
+        <v>119</v>
       </c>
       <c r="C72" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>4210</v>
+        <v>4355</v>
       </c>
       <c r="B73" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C73" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>4215</v>
+        <v>4360</v>
       </c>
       <c r="B74" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
@@ -1871,120 +1871,120 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>4220</v>
+        <v>4365</v>
       </c>
       <c r="B75" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="C75" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>4225</v>
+        <v>4370</v>
       </c>
       <c r="B76" t="n">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="C76" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>4230</v>
+        <v>4375</v>
       </c>
       <c r="B77" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>4235</v>
+        <v>4380</v>
       </c>
       <c r="B78" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C78" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>4240</v>
+        <v>4385</v>
       </c>
       <c r="B79" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="C79" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>4245</v>
+        <v>4400</v>
       </c>
       <c r="B80" t="n">
-        <v>15</v>
+        <v>98</v>
       </c>
       <c r="C80" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>4250</v>
+        <v>4410</v>
       </c>
       <c r="B81" t="n">
-        <v>181</v>
+        <v>13</v>
       </c>
       <c r="C81" t="n">
-        <v>413</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>4255</v>
+        <v>4415</v>
       </c>
       <c r="B82" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>4260</v>
+        <v>4425</v>
       </c>
       <c r="B83" t="n">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>4265</v>
+        <v>4450</v>
       </c>
       <c r="B84" t="n">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>4270</v>
+        <v>4475</v>
       </c>
       <c r="B85" t="n">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="C85" t="n">
         <v>1</v>
@@ -1992,32 +1992,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>4275</v>
+        <v>4500</v>
       </c>
       <c r="B86" t="n">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="C86" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>4280</v>
+        <v>4515</v>
       </c>
       <c r="B87" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>4285</v>
+        <v>4525</v>
       </c>
       <c r="B88" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
@@ -2025,10 +2025,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>4290</v>
+        <v>4550</v>
       </c>
       <c r="B89" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
@@ -2036,32 +2036,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>4295</v>
+        <v>4575</v>
       </c>
       <c r="B90" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="C90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>4300</v>
+        <v>4600</v>
       </c>
       <c r="B91" t="n">
-        <v>303</v>
+        <v>28</v>
       </c>
       <c r="C91" t="n">
-        <v>435</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>4305</v>
+        <v>4625</v>
       </c>
       <c r="B92" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
@@ -2069,21 +2069,21 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>4310</v>
+        <v>4650</v>
       </c>
       <c r="B93" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>4315</v>
+        <v>4675</v>
       </c>
       <c r="B94" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
@@ -2091,43 +2091,43 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>4320</v>
+        <v>4700</v>
       </c>
       <c r="B95" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>4325</v>
+        <v>4725</v>
       </c>
       <c r="B96" t="n">
-        <v>206</v>
+        <v>2</v>
       </c>
       <c r="C96" t="n">
-        <v>185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>4330</v>
+        <v>4750</v>
       </c>
       <c r="B97" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>4335</v>
+        <v>4775</v>
       </c>
       <c r="B98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -2135,21 +2135,21 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>4340</v>
+        <v>4850</v>
       </c>
       <c r="B99" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>4345</v>
+        <v>4900</v>
       </c>
       <c r="B100" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
@@ -2157,488 +2157,68 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>4350</v>
+        <v>5100</v>
       </c>
       <c r="B101" t="n">
-        <v>222</v>
+        <v>25</v>
       </c>
       <c r="C101" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>4355</v>
+        <v>5200</v>
       </c>
       <c r="B102" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="n">
-        <v>4360</v>
-      </c>
-      <c r="B103" t="n">
-        <v>5</v>
-      </c>
-      <c r="C103" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="n">
-        <v>4365</v>
-      </c>
-      <c r="B104" t="n">
-        <v>2</v>
-      </c>
-      <c r="C104" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="n">
-        <v>4370</v>
-      </c>
-      <c r="B105" t="n">
-        <v>1</v>
-      </c>
-      <c r="C105" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="n">
-        <v>4375</v>
-      </c>
-      <c r="B106" t="n">
-        <v>450</v>
-      </c>
-      <c r="C106" t="n">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="n">
-        <v>4380</v>
-      </c>
-      <c r="B107" t="n">
-        <v>5</v>
-      </c>
-      <c r="C107" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="n">
-        <v>4385</v>
-      </c>
-      <c r="B108" t="n">
-        <v>1</v>
-      </c>
-      <c r="C108" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
-        <v>4390</v>
-      </c>
-      <c r="B109" t="n">
-        <v>1</v>
-      </c>
-      <c r="C109" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
-        <v>4395</v>
-      </c>
-      <c r="B110" t="n">
-        <v>3</v>
-      </c>
-      <c r="C110" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
-        <v>4400</v>
-      </c>
-      <c r="B111" t="n">
-        <v>569</v>
-      </c>
-      <c r="C111" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="n">
-        <v>4405</v>
-      </c>
-      <c r="B112" t="n">
-        <v>1</v>
-      </c>
-      <c r="C112" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="n">
-        <v>4410</v>
-      </c>
-      <c r="B113" t="n">
-        <v>3</v>
-      </c>
-      <c r="C113" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="n">
-        <v>4415</v>
-      </c>
-      <c r="B114" t="n">
-        <v>11</v>
-      </c>
-      <c r="C114" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="n">
-        <v>4420</v>
-      </c>
-      <c r="B115" t="n">
-        <v>1</v>
-      </c>
-      <c r="C115" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="n">
-        <v>4425</v>
-      </c>
-      <c r="B116" t="n">
-        <v>249</v>
-      </c>
-      <c r="C116" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="n">
-        <v>4450</v>
-      </c>
-      <c r="B117" t="n">
-        <v>150</v>
-      </c>
-      <c r="C117" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="n">
-        <v>4455</v>
-      </c>
-      <c r="B118" t="n">
-        <v>1</v>
-      </c>
-      <c r="C118" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="n">
-        <v>4470</v>
-      </c>
-      <c r="B119" t="n">
-        <v>3</v>
-      </c>
-      <c r="C119" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="n">
-        <v>4475</v>
-      </c>
-      <c r="B120" t="n">
-        <v>76</v>
-      </c>
-      <c r="C120" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="n">
-        <v>4500</v>
-      </c>
-      <c r="B121" t="n">
-        <v>326</v>
-      </c>
-      <c r="C121" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="n">
-        <v>4510</v>
-      </c>
-      <c r="B122" t="n">
-        <v>1</v>
-      </c>
-      <c r="C122" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="n">
-        <v>4525</v>
-      </c>
-      <c r="B123" t="n">
-        <v>54</v>
-      </c>
-      <c r="C123" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="n">
-        <v>4540</v>
-      </c>
-      <c r="B124" t="n">
-        <v>1</v>
-      </c>
-      <c r="C124" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="n">
-        <v>4550</v>
-      </c>
-      <c r="B125" t="n">
-        <v>371</v>
-      </c>
-      <c r="C125" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="n">
-        <v>4560</v>
-      </c>
-      <c r="B126" t="n">
-        <v>1</v>
-      </c>
-      <c r="C126" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="n">
-        <v>4575</v>
-      </c>
-      <c r="B127" t="n">
-        <v>31</v>
-      </c>
-      <c r="C127" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="n">
-        <v>4590</v>
-      </c>
-      <c r="B128" t="n">
-        <v>0</v>
-      </c>
-      <c r="C128" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="n">
-        <v>4600</v>
-      </c>
-      <c r="B129" t="n">
-        <v>319</v>
-      </c>
-      <c r="C129" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="n">
-        <v>4625</v>
-      </c>
-      <c r="B130" t="n">
-        <v>29</v>
-      </c>
-      <c r="C130" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="n">
-        <v>4650</v>
-      </c>
-      <c r="B131" t="n">
-        <v>76</v>
-      </c>
-      <c r="C131" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="n">
-        <v>4675</v>
-      </c>
-      <c r="B132" t="n">
-        <v>15</v>
-      </c>
-      <c r="C132" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="n">
-        <v>4700</v>
-      </c>
-      <c r="B133" t="n">
-        <v>36</v>
-      </c>
-      <c r="C133" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="n">
-        <v>4725</v>
-      </c>
-      <c r="B134" t="n">
-        <v>18</v>
-      </c>
-      <c r="C134" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="n">
-        <v>4750</v>
-      </c>
-      <c r="B135" t="n">
-        <v>104</v>
-      </c>
-      <c r="C135" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="n">
-        <v>4775</v>
-      </c>
-      <c r="B136" t="n">
-        <v>28</v>
-      </c>
-      <c r="C136" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="n">
-        <v>4800</v>
-      </c>
-      <c r="B137" t="n">
-        <v>57</v>
-      </c>
-      <c r="C137" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="n">
-        <v>4850</v>
-      </c>
-      <c r="B138" t="n">
-        <v>101</v>
-      </c>
-      <c r="C138" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="n">
-        <v>4875</v>
-      </c>
-      <c r="B139" t="n">
-        <v>27</v>
-      </c>
-      <c r="C139" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="n">
-        <v>4900</v>
-      </c>
-      <c r="B140" t="n">
-        <v>8</v>
-      </c>
-      <c r="C140" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="n">
-        <v>5000</v>
-      </c>
-      <c r="B141" t="n">
-        <v>5</v>
-      </c>
-      <c r="C141" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="n">
-        <v>5100</v>
-      </c>
-      <c r="B142" t="n">
-        <v>6</v>
-      </c>
-      <c r="C142" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="n">
-        <v>5200</v>
-      </c>
-      <c r="B143" t="n">
-        <v>15</v>
-      </c>
-      <c r="C143" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="n">
-        <v>10000</v>
-      </c>
-      <c r="B144" t="n">
-        <v>0</v>
-      </c>
-      <c r="C144" t="n">
-        <v>0</v>
-      </c>
-    </row>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
     <row r="145"/>
     <row r="146"/>
     <row r="147"/>
@@ -2820,7 +2400,7 @@
         </is>
       </c>
       <c r="F4" s="30" t="n">
-        <v>4186.7</v>
+        <v>4162.3</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="29">
@@ -5916,7 +5496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6266,9 +5846,97 @@
         </is>
       </c>
       <c r="K8" s="43" t="n">
-        <v>46297.40944206915</v>
+        <v>46297.40944207176</v>
       </c>
       <c r="L8" t="inlineStr">
+        <is>
+          <t>DEC 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="35" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MW1 Week 1 - OCT 2026 (V26)</t>
+        </is>
+      </c>
+      <c r="C9" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="42" t="n">
+        <v>4162.3</v>
+      </c>
+      <c r="E9" s="36" t="n">
+        <v>4215</v>
+      </c>
+      <c r="F9" s="38" t="n">
+        <v>0.01266126900992235</v>
+      </c>
+      <c r="G9" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" s="39" t="n">
+        <v>0.7856942496493688</v>
+      </c>
+      <c r="I9" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>PRELIMINARY</t>
+        </is>
+      </c>
+      <c r="K9" s="43" t="n">
+        <v>46300.378576875</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>DEC 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="35" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>AB1 Week 1 - OCT 2026 (V26)</t>
+        </is>
+      </c>
+      <c r="C10" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="42" t="n">
+        <v>4162.3</v>
+      </c>
+      <c r="E10" s="36" t="n">
+        <v>4200</v>
+      </c>
+      <c r="F10" s="38" t="n">
+        <v>0.009057492251879927</v>
+      </c>
+      <c r="G10" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="39" t="n">
+        <v>0.8313321898227558</v>
+      </c>
+      <c r="I10" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>FINAL</t>
+        </is>
+      </c>
+      <c r="K10" s="43" t="n">
+        <v>46301.38472030024</v>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>DEC 26</t>
         </is>

--- a/คำนวน_max_pain_10 (2).xlsx
+++ b/คำนวน_max_pain_10 (2).xlsx
@@ -1007,7 +1007,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="F2" s="26" t="inlineStr">
         <is>
-          <t>AB1 Week 1 - OCT 2026 (V26)</t>
+          <t>WD1 Week 1 - OCT 2026 (V26)</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -1027,13 +1027,13 @@
     </row>
     <row r="3" ht="25.5" customHeight="1" s="29">
       <c r="A3" s="2" t="n">
-        <v>3850</v>
+        <v>3800</v>
       </c>
       <c r="B3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="F3" s="27" t="n">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
@@ -1051,13 +1051,13 @@
     </row>
     <row r="4" ht="25.5" customHeight="1" s="29">
       <c r="A4" s="2" t="n">
-        <v>3875</v>
+        <v>3830</v>
       </c>
       <c r="B4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="F4" s="26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
@@ -1075,13 +1075,13 @@
     </row>
     <row r="5" ht="25.5" customHeight="1" s="29">
       <c r="A5" s="2" t="n">
-        <v>3895</v>
+        <v>3900</v>
       </c>
       <c r="B5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="F5" s="26" t="n">
-        <v>1749</v>
+        <v>3129</v>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
@@ -1099,13 +1099,13 @@
     </row>
     <row r="6" ht="25.5" customHeight="1" s="29">
       <c r="A6" s="2" t="n">
-        <v>3900</v>
+        <v>3910</v>
       </c>
       <c r="B6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="F6" s="26" t="n">
-        <v>1454</v>
+        <v>2068</v>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
@@ -1123,13 +1123,13 @@
     </row>
     <row r="7" ht="15" customHeight="1" s="29">
       <c r="A7" s="2" t="n">
-        <v>3915</v>
+        <v>3925</v>
       </c>
       <c r="B7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="29">
@@ -1140,287 +1140,287 @@
         <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="29">
       <c r="A9" s="2" t="n">
-        <v>3960</v>
+        <v>3955</v>
       </c>
       <c r="B9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="29">
       <c r="A10" s="2" t="n">
-        <v>3975</v>
+        <v>3960</v>
       </c>
       <c r="B10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="29">
       <c r="A11" s="2" t="n">
-        <v>3980</v>
+        <v>3970</v>
       </c>
       <c r="B11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="29">
       <c r="A12" s="2" t="n">
-        <v>3995</v>
+        <v>3975</v>
       </c>
       <c r="B12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="29">
       <c r="A13" s="2" t="n">
-        <v>4000</v>
+        <v>3980</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>52</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="29">
       <c r="A14" s="2" t="n">
-        <v>4025</v>
+        <v>3995</v>
       </c>
       <c r="B14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="29">
       <c r="A15" s="2" t="n">
-        <v>4035</v>
+        <v>4000</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="29">
       <c r="A16" s="2" t="n">
-        <v>4045</v>
+        <v>4005</v>
       </c>
       <c r="B16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="29">
       <c r="A17" s="2" t="n">
-        <v>4050</v>
+        <v>4010</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="29">
       <c r="A18" s="2" t="n">
-        <v>4055</v>
+        <v>4020</v>
       </c>
       <c r="B18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="29">
       <c r="A19" s="2" t="n">
-        <v>4060</v>
+        <v>4025</v>
       </c>
       <c r="B19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>80</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="29">
       <c r="A20" s="2" t="n">
-        <v>4065</v>
+        <v>4035</v>
       </c>
       <c r="B20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="29">
       <c r="A21" s="2" t="n">
-        <v>4070</v>
+        <v>4040</v>
       </c>
       <c r="B21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="29">
       <c r="A22" s="2" t="n">
-        <v>4075</v>
+        <v>4045</v>
       </c>
       <c r="B22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="29">
       <c r="A23" s="2" t="n">
-        <v>4080</v>
+        <v>4050</v>
       </c>
       <c r="B23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="29">
       <c r="A24" s="2" t="n">
-        <v>4085</v>
+        <v>4055</v>
       </c>
       <c r="B24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="29">
       <c r="A25" s="2" t="n">
-        <v>4090</v>
+        <v>4060</v>
       </c>
       <c r="B25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="29">
       <c r="A26" s="2" t="n">
-        <v>4100</v>
+        <v>4065</v>
       </c>
       <c r="B26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>259</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="29">
       <c r="A27" s="2" t="n">
-        <v>4105</v>
+        <v>4070</v>
       </c>
       <c r="B27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="29">
       <c r="A28" s="2" t="n">
-        <v>4110</v>
+        <v>4075</v>
       </c>
       <c r="B28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>9</v>
+        <v>117</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="29">
       <c r="A29" s="2" t="n">
-        <v>4115</v>
+        <v>4080</v>
       </c>
       <c r="B29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="29">
       <c r="A30" s="2" t="n">
-        <v>4120</v>
+        <v>4085</v>
       </c>
       <c r="B30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="29">
       <c r="A31" s="2" t="n">
-        <v>4125</v>
+        <v>4090</v>
       </c>
       <c r="B31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>101</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="29">
       <c r="A32" s="2" t="n">
-        <v>4135</v>
+        <v>4095</v>
       </c>
       <c r="B32" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="29">
       <c r="A33" s="2" t="n">
-        <v>4140</v>
+        <v>4100</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>40</v>
+        <v>375</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="29">
       <c r="A34" s="2" t="n">
-        <v>4145</v>
+        <v>4105</v>
       </c>
       <c r="B34" s="3" t="n">
         <v>0</v>
@@ -1431,241 +1431,241 @@
     </row>
     <row r="35" ht="15" customHeight="1" s="29">
       <c r="A35" s="2" t="n">
-        <v>4150</v>
+        <v>4110</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="29">
       <c r="A36" s="2" t="n">
-        <v>4155</v>
+        <v>4115</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="29">
       <c r="A37" s="2" t="n">
-        <v>4160</v>
+        <v>4120</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="29">
       <c r="A38" s="2" t="n">
-        <v>4165</v>
+        <v>4125</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="29">
       <c r="A39" s="2" t="n">
-        <v>4170</v>
+        <v>4130</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1</v>
+        <v>104</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="29">
       <c r="A40" s="2" t="n">
-        <v>4175</v>
+        <v>4135</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="29">
       <c r="A41" s="2" t="n">
-        <v>4180</v>
+        <v>4140</v>
       </c>
       <c r="B41" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="29">
       <c r="A42" s="2" t="n">
-        <v>4185</v>
+        <v>4145</v>
       </c>
       <c r="B42" s="3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="29">
       <c r="A43" s="2" t="n">
-        <v>4190</v>
+        <v>4150</v>
       </c>
       <c r="B43" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>2</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="29">
       <c r="A44" s="2" t="n">
-        <v>4195</v>
+        <v>4155</v>
       </c>
       <c r="B44" s="3" t="n">
-        <v>111</v>
+        <v>3</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="29">
       <c r="A45" s="2" t="n">
-        <v>4200</v>
+        <v>4160</v>
       </c>
       <c r="B45" s="3" t="n">
-        <v>152</v>
+        <v>8</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="29">
       <c r="A46" s="2" t="n">
-        <v>4205</v>
+        <v>4165</v>
       </c>
       <c r="B46" s="3" t="n">
-        <v>10</v>
+        <v>85</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="29">
       <c r="A47" s="2" t="n">
-        <v>4210</v>
+        <v>4170</v>
       </c>
       <c r="B47" s="3" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="29">
       <c r="A48" s="2" t="n">
-        <v>4215</v>
+        <v>4175</v>
       </c>
       <c r="B48" s="3" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="29">
       <c r="A49" s="2" t="n">
-        <v>4220</v>
+        <v>4180</v>
       </c>
       <c r="B49" s="3" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>9</v>
+        <v>70</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="29">
       <c r="A50" s="2" t="n">
-        <v>4225</v>
+        <v>4185</v>
       </c>
       <c r="B50" s="3" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>63</v>
+        <v>135</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="29">
       <c r="A51" s="2" t="n">
-        <v>4230</v>
+        <v>4190</v>
       </c>
       <c r="B51" s="3" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="29">
       <c r="A52" s="2" t="n">
-        <v>4235</v>
+        <v>4195</v>
       </c>
       <c r="B52" s="3" t="n">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>4240</v>
+        <v>4200</v>
       </c>
       <c r="B53" s="3" t="n">
-        <v>12</v>
+        <v>109</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="29">
       <c r="A54" s="2" t="n">
-        <v>4245</v>
+        <v>4205</v>
       </c>
       <c r="B54" s="3" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="29">
       <c r="A55" s="2" t="n">
-        <v>4250</v>
+        <v>4210</v>
       </c>
       <c r="B55" s="3" t="n">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="29">
       <c r="A56" s="2" t="n">
-        <v>4255</v>
+        <v>4215</v>
       </c>
       <c r="B56" s="3" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C56" s="3" t="n">
         <v>0</v>
@@ -1673,32 +1673,32 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>4260</v>
+        <v>4220</v>
       </c>
       <c r="B57" s="3" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>4265</v>
+        <v>4225</v>
       </c>
       <c r="B58" s="3" t="n">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>4270</v>
+        <v>4230</v>
       </c>
       <c r="B59" s="3" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="C59" s="3" t="n">
         <v>0</v>
@@ -1706,21 +1706,21 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>4275</v>
+        <v>4235</v>
       </c>
       <c r="B60" s="3" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>4280</v>
+        <v>4240</v>
       </c>
       <c r="B61" s="3" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="C61" s="3" t="n">
         <v>0</v>
@@ -1728,32 +1728,32 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>4285</v>
+        <v>4245</v>
       </c>
       <c r="B62" s="3" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>4300</v>
+        <v>4250</v>
       </c>
       <c r="B63" t="n">
-        <v>67</v>
+        <v>321</v>
       </c>
       <c r="C63" t="n">
-        <v>57</v>
+        <v>40</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>4305</v>
+        <v>4255</v>
       </c>
       <c r="B64" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
@@ -1761,32 +1761,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>4310</v>
+        <v>4260</v>
       </c>
       <c r="B65" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>4315</v>
+        <v>4265</v>
       </c>
       <c r="B66" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>4320</v>
+        <v>4270</v>
       </c>
       <c r="B67" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
@@ -1794,32 +1794,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>4325</v>
+        <v>4275</v>
       </c>
       <c r="B68" t="n">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="C68" t="n">
-        <v>4</v>
+        <v>162</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>4330</v>
+        <v>4280</v>
       </c>
       <c r="B69" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>4340</v>
+        <v>4285</v>
       </c>
       <c r="B70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
@@ -1827,10 +1827,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>4345</v>
+        <v>4290</v>
       </c>
       <c r="B71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
@@ -1838,10 +1838,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>4350</v>
+        <v>4295</v>
       </c>
       <c r="B72" t="n">
-        <v>119</v>
+        <v>3</v>
       </c>
       <c r="C72" t="n">
         <v>2</v>
@@ -1849,21 +1849,21 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>4355</v>
+        <v>4300</v>
       </c>
       <c r="B73" t="n">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>4360</v>
+        <v>4305</v>
       </c>
       <c r="B74" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
@@ -1871,10 +1871,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>4365</v>
+        <v>4310</v>
       </c>
       <c r="B75" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
@@ -1882,10 +1882,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>4370</v>
+        <v>4315</v>
       </c>
       <c r="B76" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
@@ -1893,54 +1893,54 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>4375</v>
+        <v>4320</v>
       </c>
       <c r="B77" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>4380</v>
+        <v>4325</v>
       </c>
       <c r="B78" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>4385</v>
+        <v>4330</v>
       </c>
       <c r="B79" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>4400</v>
+        <v>4335</v>
       </c>
       <c r="B80" t="n">
-        <v>98</v>
+        <v>5</v>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>4410</v>
+        <v>4345</v>
       </c>
       <c r="B81" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
@@ -1948,21 +1948,21 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>4415</v>
+        <v>4350</v>
       </c>
       <c r="B82" t="n">
-        <v>5</v>
+        <v>401</v>
       </c>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>4425</v>
+        <v>4365</v>
       </c>
       <c r="B83" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
@@ -1970,32 +1970,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>4450</v>
+        <v>4375</v>
       </c>
       <c r="B84" t="n">
-        <v>59</v>
+        <v>115</v>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>4475</v>
+        <v>4400</v>
       </c>
       <c r="B85" t="n">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>4500</v>
+        <v>4425</v>
       </c>
       <c r="B86" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
@@ -2003,21 +2003,21 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>4515</v>
+        <v>4450</v>
       </c>
       <c r="B87" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>4525</v>
+        <v>4475</v>
       </c>
       <c r="B88" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
@@ -2025,10 +2025,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>4550</v>
+        <v>4500</v>
       </c>
       <c r="B89" t="n">
-        <v>7</v>
+        <v>172</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
@@ -2036,21 +2036,21 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>4575</v>
+        <v>4525</v>
       </c>
       <c r="B90" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>4600</v>
+        <v>4550</v>
       </c>
       <c r="B91" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
@@ -2058,10 +2058,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>4625</v>
+        <v>4575</v>
       </c>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
@@ -2069,10 +2069,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>4650</v>
+        <v>4600</v>
       </c>
       <c r="B93" t="n">
-        <v>19</v>
+        <v>254</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
@@ -2080,10 +2080,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>4675</v>
+        <v>4625</v>
       </c>
       <c r="B94" t="n">
-        <v>3</v>
+        <v>256</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
@@ -2091,10 +2091,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>4700</v>
+        <v>4650</v>
       </c>
       <c r="B95" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>4725</v>
+        <v>4675</v>
       </c>
       <c r="B96" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>4750</v>
+        <v>4700</v>
       </c>
       <c r="B97" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
@@ -2124,10 +2124,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>4775</v>
+        <v>4725</v>
       </c>
       <c r="B98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -2135,7 +2135,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>4850</v>
+        <v>4750</v>
       </c>
       <c r="B99" t="n">
         <v>1</v>
@@ -2146,10 +2146,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>4900</v>
+        <v>4825</v>
       </c>
       <c r="B100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
@@ -2157,10 +2157,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>5100</v>
+        <v>4850</v>
       </c>
       <c r="B101" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
@@ -2168,10 +2168,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>5200</v>
+        <v>5100</v>
       </c>
       <c r="B102" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
@@ -2400,7 +2400,7 @@
         </is>
       </c>
       <c r="F4" s="30" t="n">
-        <v>4162.3</v>
+        <v>4187.1</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="29">
@@ -5496,7 +5496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5934,9 +5934,53 @@
         </is>
       </c>
       <c r="K10" s="43" t="n">
-        <v>46301.38472030024</v>
+        <v>46301.38472030093</v>
       </c>
       <c r="L10" t="inlineStr">
+        <is>
+          <t>DEC 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="35" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>WD1 Week 1 - OCT 2026 (V26)</t>
+        </is>
+      </c>
+      <c r="C11" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="42" t="n">
+        <v>4187.1</v>
+      </c>
+      <c r="E11" s="36" t="n">
+        <v>4200</v>
+      </c>
+      <c r="F11" s="38" t="n">
+        <v>0.003080891309020476</v>
+      </c>
+      <c r="G11" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" s="39" t="n">
+        <v>0.6609140300415468</v>
+      </c>
+      <c r="I11" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>PRELIMINARY</t>
+        </is>
+      </c>
+      <c r="K11" s="43" t="n">
+        <v>46302.53311725874</v>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>DEC 26</t>
         </is>

--- a/คำนวน_max_pain_10 (2).xlsx
+++ b/คำนวน_max_pain_10 (2).xlsx
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="K11" s="43" t="n">
-        <v>46302.53311725874</v>
+        <v>46302.58533634283</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>

--- a/คำนวน_max_pain_10 (2).xlsx
+++ b/คำนวน_max_pain_10 (2).xlsx
@@ -715,12 +715,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Max Pain Calc'!$A$2:$A$102</f>
+              <f>'Max Pain Calc'!$A$2:$A$134</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Max Pain Calc'!$B$2:$B$102</f>
+              <f>'Max Pain Calc'!$B$2:$B$134</f>
             </numRef>
           </val>
         </ser>
@@ -1001,13 +1001,13 @@
     </row>
     <row r="2" ht="25.5" customHeight="1" s="29">
       <c r="A2" s="2" t="n">
-        <v>3750</v>
+        <v>3000</v>
       </c>
       <c r="B2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="F2" s="26" t="inlineStr">
         <is>
-          <t>WD1 Week 1 - OCT 2026 (V26)</t>
+          <t>E21 Week 2 - OCT 2026 (V26)</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -1027,13 +1027,13 @@
     </row>
     <row r="3" ht="25.5" customHeight="1" s="29">
       <c r="A3" s="2" t="n">
-        <v>3800</v>
+        <v>3250</v>
       </c>
       <c r="B3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="F3" s="27" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
@@ -1051,13 +1051,13 @@
     </row>
     <row r="4" ht="25.5" customHeight="1" s="29">
       <c r="A4" s="2" t="n">
-        <v>3830</v>
+        <v>3500</v>
       </c>
       <c r="B4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>4</v>
+        <v>133</v>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="F4" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
@@ -1075,13 +1075,13 @@
     </row>
     <row r="5" ht="25.5" customHeight="1" s="29">
       <c r="A5" s="2" t="n">
-        <v>3900</v>
+        <v>3600</v>
       </c>
       <c r="B5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="F5" s="26" t="n">
-        <v>3129</v>
+        <v>6721</v>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
@@ -1099,13 +1099,13 @@
     </row>
     <row r="6" ht="25.5" customHeight="1" s="29">
       <c r="A6" s="2" t="n">
-        <v>3910</v>
+        <v>3700</v>
       </c>
       <c r="B6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="F6" s="26" t="n">
-        <v>2068</v>
+        <v>5835</v>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
@@ -1123,18 +1123,18 @@
     </row>
     <row r="7" ht="15" customHeight="1" s="29">
       <c r="A7" s="2" t="n">
-        <v>3925</v>
+        <v>3750</v>
       </c>
       <c r="B7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="29">
       <c r="A8" s="2" t="n">
-        <v>3950</v>
+        <v>3775</v>
       </c>
       <c r="B8" s="3" t="n">
         <v>0</v>
@@ -1145,7 +1145,7 @@
     </row>
     <row r="9" ht="15" customHeight="1" s="29">
       <c r="A9" s="2" t="n">
-        <v>3955</v>
+        <v>3780</v>
       </c>
       <c r="B9" s="3" t="n">
         <v>0</v>
@@ -1156,73 +1156,73 @@
     </row>
     <row r="10" ht="15" customHeight="1" s="29">
       <c r="A10" s="2" t="n">
-        <v>3960</v>
+        <v>3795</v>
       </c>
       <c r="B10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="29">
       <c r="A11" s="2" t="n">
-        <v>3970</v>
+        <v>3800</v>
       </c>
       <c r="B11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>2</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="29">
       <c r="A12" s="2" t="n">
-        <v>3975</v>
+        <v>3810</v>
       </c>
       <c r="B12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="29">
       <c r="A13" s="2" t="n">
-        <v>3980</v>
+        <v>3825</v>
       </c>
       <c r="B13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="29">
       <c r="A14" s="2" t="n">
-        <v>3995</v>
+        <v>3830</v>
       </c>
       <c r="B14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="29">
       <c r="A15" s="2" t="n">
-        <v>4000</v>
+        <v>3850</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="29">
       <c r="A16" s="2" t="n">
-        <v>4005</v>
+        <v>3855</v>
       </c>
       <c r="B16" s="3" t="n">
         <v>0</v>
@@ -1233,659 +1233,659 @@
     </row>
     <row r="17" ht="15" customHeight="1" s="29">
       <c r="A17" s="2" t="n">
-        <v>4010</v>
+        <v>3865</v>
       </c>
       <c r="B17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="29">
       <c r="A18" s="2" t="n">
-        <v>4020</v>
+        <v>3880</v>
       </c>
       <c r="B18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="29">
       <c r="A19" s="2" t="n">
-        <v>4025</v>
+        <v>3890</v>
       </c>
       <c r="B19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="29">
       <c r="A20" s="2" t="n">
-        <v>4035</v>
+        <v>3900</v>
       </c>
       <c r="B20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>4</v>
+        <v>173</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="29">
       <c r="A21" s="2" t="n">
-        <v>4040</v>
+        <v>3915</v>
       </c>
       <c r="B21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="29">
       <c r="A22" s="2" t="n">
-        <v>4045</v>
+        <v>3925</v>
       </c>
       <c r="B22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="29">
       <c r="A23" s="2" t="n">
-        <v>4050</v>
+        <v>3930</v>
       </c>
       <c r="B23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="29">
       <c r="A24" s="2" t="n">
-        <v>4055</v>
+        <v>3945</v>
       </c>
       <c r="B24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="29">
       <c r="A25" s="2" t="n">
-        <v>4060</v>
+        <v>3950</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>9</v>
+        <v>342</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="29">
       <c r="A26" s="2" t="n">
-        <v>4065</v>
+        <v>3955</v>
       </c>
       <c r="B26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="29">
       <c r="A27" s="2" t="n">
-        <v>4070</v>
+        <v>3960</v>
       </c>
       <c r="B27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="29">
       <c r="A28" s="2" t="n">
-        <v>4075</v>
+        <v>3970</v>
       </c>
       <c r="B28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>117</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="29">
       <c r="A29" s="2" t="n">
-        <v>4080</v>
+        <v>3975</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>8</v>
+        <v>147</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="29">
       <c r="A30" s="2" t="n">
-        <v>4085</v>
+        <v>3980</v>
       </c>
       <c r="B30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="29">
       <c r="A31" s="2" t="n">
-        <v>4090</v>
+        <v>3985</v>
       </c>
       <c r="B31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="29">
       <c r="A32" s="2" t="n">
-        <v>4095</v>
+        <v>3990</v>
       </c>
       <c r="B32" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="29">
       <c r="A33" s="2" t="n">
-        <v>4100</v>
+        <v>3995</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>375</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="29">
       <c r="A34" s="2" t="n">
-        <v>4105</v>
+        <v>4000</v>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>11</v>
+        <v>841</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="29">
       <c r="A35" s="2" t="n">
-        <v>4110</v>
+        <v>4005</v>
       </c>
       <c r="B35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="29">
       <c r="A36" s="2" t="n">
-        <v>4115</v>
+        <v>4010</v>
       </c>
       <c r="B36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="29">
       <c r="A37" s="2" t="n">
-        <v>4120</v>
+        <v>4015</v>
       </c>
       <c r="B37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="29">
       <c r="A38" s="2" t="n">
-        <v>4125</v>
+        <v>4020</v>
       </c>
       <c r="B38" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="29">
       <c r="A39" s="2" t="n">
-        <v>4130</v>
+        <v>4025</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="29">
       <c r="A40" s="2" t="n">
-        <v>4135</v>
+        <v>4030</v>
       </c>
       <c r="B40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="29">
       <c r="A41" s="2" t="n">
-        <v>4140</v>
+        <v>4035</v>
       </c>
       <c r="B41" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="29">
       <c r="A42" s="2" t="n">
-        <v>4145</v>
+        <v>4040</v>
       </c>
       <c r="B42" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="29">
       <c r="A43" s="2" t="n">
-        <v>4150</v>
+        <v>4045</v>
       </c>
       <c r="B43" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>70</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="29">
       <c r="A44" s="2" t="n">
-        <v>4155</v>
+        <v>4050</v>
       </c>
       <c r="B44" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>66</v>
+        <v>781</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="29">
       <c r="A45" s="2" t="n">
-        <v>4160</v>
+        <v>4055</v>
       </c>
       <c r="B45" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>53</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="29">
       <c r="A46" s="2" t="n">
-        <v>4165</v>
+        <v>4060</v>
       </c>
       <c r="B46" s="3" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="29">
       <c r="A47" s="2" t="n">
-        <v>4170</v>
+        <v>4065</v>
       </c>
       <c r="B47" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="29">
       <c r="A48" s="2" t="n">
-        <v>4175</v>
+        <v>4070</v>
       </c>
       <c r="B48" s="3" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>73</v>
+        <v>24</v>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="29">
       <c r="A49" s="2" t="n">
-        <v>4180</v>
+        <v>4075</v>
       </c>
       <c r="B49" s="3" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>70</v>
+        <v>353</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="29">
       <c r="A50" s="2" t="n">
-        <v>4185</v>
+        <v>4080</v>
       </c>
       <c r="B50" s="3" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>135</v>
+        <v>26</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="29">
       <c r="A51" s="2" t="n">
-        <v>4190</v>
+        <v>4085</v>
       </c>
       <c r="B51" s="3" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="29">
       <c r="A52" s="2" t="n">
-        <v>4195</v>
+        <v>4090</v>
       </c>
       <c r="B52" s="3" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>4200</v>
+        <v>4095</v>
       </c>
       <c r="B53" s="3" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>57</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="29">
       <c r="A54" s="2" t="n">
-        <v>4205</v>
+        <v>4100</v>
       </c>
       <c r="B54" s="3" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>6</v>
+        <v>719</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="29">
       <c r="A55" s="2" t="n">
-        <v>4210</v>
+        <v>4105</v>
       </c>
       <c r="B55" s="3" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="29">
       <c r="A56" s="2" t="n">
-        <v>4215</v>
+        <v>4110</v>
       </c>
       <c r="B56" s="3" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>4220</v>
+        <v>4115</v>
       </c>
       <c r="B57" s="3" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>4225</v>
+        <v>4120</v>
       </c>
       <c r="B58" s="3" t="n">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>4230</v>
+        <v>4125</v>
       </c>
       <c r="B59" s="3" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>4235</v>
+        <v>4130</v>
       </c>
       <c r="B60" s="3" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>4240</v>
+        <v>4135</v>
       </c>
       <c r="B61" s="3" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>4245</v>
+        <v>4140</v>
       </c>
       <c r="B62" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>1</v>
+        <v>211</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>4250</v>
+        <v>4145</v>
       </c>
       <c r="B63" t="n">
-        <v>321</v>
+        <v>8</v>
       </c>
       <c r="C63" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>4255</v>
+        <v>4150</v>
       </c>
       <c r="B64" t="n">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>318</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>4260</v>
+        <v>4155</v>
       </c>
       <c r="B65" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>4265</v>
+        <v>4160</v>
       </c>
       <c r="B66" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>4270</v>
+        <v>4165</v>
       </c>
       <c r="B67" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>4275</v>
+        <v>4170</v>
       </c>
       <c r="B68" t="n">
-        <v>154</v>
+        <v>36</v>
       </c>
       <c r="C68" t="n">
-        <v>162</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>4280</v>
+        <v>4175</v>
       </c>
       <c r="B69" t="n">
-        <v>11</v>
+        <v>112</v>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>4285</v>
+        <v>4180</v>
       </c>
       <c r="B70" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>4290</v>
+        <v>4185</v>
       </c>
       <c r="B71" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>4295</v>
+        <v>4190</v>
       </c>
       <c r="B72" t="n">
-        <v>3</v>
+        <v>162</v>
       </c>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>4300</v>
+        <v>4195</v>
       </c>
       <c r="B73" t="n">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="C73" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>4305</v>
+        <v>4200</v>
       </c>
       <c r="B74" t="n">
-        <v>2</v>
+        <v>581</v>
       </c>
       <c r="C74" t="n">
-        <v>0</v>
+        <v>278</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>4310</v>
+        <v>4205</v>
       </c>
       <c r="B75" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>4315</v>
+        <v>4210</v>
       </c>
       <c r="B76" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
@@ -1893,43 +1893,43 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>4320</v>
+        <v>4215</v>
       </c>
       <c r="B77" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>4325</v>
+        <v>4220</v>
       </c>
       <c r="B78" t="n">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="C78" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>4330</v>
+        <v>4225</v>
       </c>
       <c r="B79" t="n">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>73</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>4335</v>
+        <v>4230</v>
       </c>
       <c r="B80" t="n">
-        <v>5</v>
+        <v>145</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
@@ -1937,10 +1937,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>4345</v>
+        <v>4235</v>
       </c>
       <c r="B81" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
@@ -1948,21 +1948,21 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>4350</v>
+        <v>4240</v>
       </c>
       <c r="B82" t="n">
-        <v>401</v>
+        <v>12</v>
       </c>
       <c r="C82" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>4365</v>
+        <v>4245</v>
       </c>
       <c r="B83" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
@@ -1970,32 +1970,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>4375</v>
+        <v>4250</v>
       </c>
       <c r="B84" t="n">
-        <v>115</v>
+        <v>343</v>
       </c>
       <c r="C84" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>4400</v>
+        <v>4255</v>
       </c>
       <c r="B85" t="n">
-        <v>223</v>
+        <v>18</v>
       </c>
       <c r="C85" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>4425</v>
+        <v>4260</v>
       </c>
       <c r="B86" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
@@ -2003,10 +2003,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>4450</v>
+        <v>4265</v>
       </c>
       <c r="B87" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -2014,10 +2014,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>4475</v>
+        <v>4270</v>
       </c>
       <c r="B88" t="n">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
@@ -2025,21 +2025,21 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>4500</v>
+        <v>4275</v>
       </c>
       <c r="B89" t="n">
-        <v>172</v>
+        <v>270</v>
       </c>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>4525</v>
+        <v>4280</v>
       </c>
       <c r="B90" t="n">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
@@ -2047,21 +2047,21 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>4550</v>
+        <v>4285</v>
       </c>
       <c r="B91" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>4575</v>
+        <v>4290</v>
       </c>
       <c r="B92" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
@@ -2069,21 +2069,21 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>4600</v>
+        <v>4300</v>
       </c>
       <c r="B93" t="n">
-        <v>254</v>
+        <v>581</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>4625</v>
+        <v>4305</v>
       </c>
       <c r="B94" t="n">
-        <v>256</v>
+        <v>9</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
@@ -2091,10 +2091,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>4650</v>
+        <v>4310</v>
       </c>
       <c r="B95" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
@@ -2102,113 +2102,433 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>4675</v>
+        <v>4315</v>
       </c>
       <c r="B96" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>4700</v>
+        <v>4320</v>
       </c>
       <c r="B97" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>4725</v>
+        <v>4325</v>
       </c>
       <c r="B98" t="n">
-        <v>3</v>
+        <v>135</v>
       </c>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>4750</v>
+        <v>4330</v>
       </c>
       <c r="B99" t="n">
+        <v>21</v>
+      </c>
+      <c r="C99" t="n">
         <v>1</v>
-      </c>
-      <c r="C99" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>4825</v>
+        <v>4340</v>
       </c>
       <c r="B100" t="n">
+        <v>7</v>
+      </c>
+      <c r="C100" t="n">
         <v>1</v>
-      </c>
-      <c r="C100" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>4850</v>
+        <v>4350</v>
       </c>
       <c r="B101" t="n">
-        <v>5</v>
+        <v>313</v>
       </c>
       <c r="C101" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
+        <v>4355</v>
+      </c>
+      <c r="B102" t="n">
+        <v>5</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>4360</v>
+      </c>
+      <c r="B103" t="n">
+        <v>5</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>4370</v>
+      </c>
+      <c r="B104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>4375</v>
+      </c>
+      <c r="B105" t="n">
+        <v>64</v>
+      </c>
+      <c r="C105" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>4380</v>
+      </c>
+      <c r="B106" t="n">
+        <v>4</v>
+      </c>
+      <c r="C106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>4400</v>
+      </c>
+      <c r="B107" t="n">
+        <v>634</v>
+      </c>
+      <c r="C107" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>4405</v>
+      </c>
+      <c r="B108" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>4425</v>
+      </c>
+      <c r="B109" t="n">
+        <v>516</v>
+      </c>
+      <c r="C109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>4440</v>
+      </c>
+      <c r="B110" t="n">
+        <v>1</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>4450</v>
+      </c>
+      <c r="B111" t="n">
+        <v>100</v>
+      </c>
+      <c r="C111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>4465</v>
+      </c>
+      <c r="B112" t="n">
+        <v>6</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>4475</v>
+      </c>
+      <c r="B113" t="n">
+        <v>429</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>4500</v>
+      </c>
+      <c r="B114" t="n">
+        <v>540</v>
+      </c>
+      <c r="C114" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>4525</v>
+      </c>
+      <c r="B115" t="n">
+        <v>57</v>
+      </c>
+      <c r="C115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>4535</v>
+      </c>
+      <c r="B116" t="n">
+        <v>1</v>
+      </c>
+      <c r="C116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>4550</v>
+      </c>
+      <c r="B117" t="n">
+        <v>72</v>
+      </c>
+      <c r="C117" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>4575</v>
+      </c>
+      <c r="B118" t="n">
+        <v>66</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>4600</v>
+      </c>
+      <c r="B119" t="n">
+        <v>79</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>4625</v>
+      </c>
+      <c r="B120" t="n">
+        <v>45</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>4650</v>
+      </c>
+      <c r="B121" t="n">
+        <v>27</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>4675</v>
+      </c>
+      <c r="B122" t="n">
+        <v>32</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>4700</v>
+      </c>
+      <c r="B123" t="n">
+        <v>23</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>4725</v>
+      </c>
+      <c r="B124" t="n">
+        <v>30</v>
+      </c>
+      <c r="C124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>4750</v>
+      </c>
+      <c r="B125" t="n">
+        <v>45</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>4775</v>
+      </c>
+      <c r="B126" t="n">
+        <v>29</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>4800</v>
+      </c>
+      <c r="B127" t="n">
+        <v>7</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>4850</v>
+      </c>
+      <c r="B128" t="n">
+        <v>5</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>4900</v>
+      </c>
+      <c r="B129" t="n">
+        <v>19</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>5000</v>
+      </c>
+      <c r="B130" t="n">
+        <v>172</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
         <v>5100</v>
       </c>
-      <c r="B102" t="n">
-        <v>8</v>
-      </c>
-      <c r="C102" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
+      <c r="B131" t="n">
+        <v>97</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>5200</v>
+      </c>
+      <c r="B132" t="n">
+        <v>41</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>5250</v>
+      </c>
+      <c r="B133" t="n">
+        <v>6</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>10000</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="135"/>
     <row r="136"/>
     <row r="137"/>
@@ -2400,7 +2720,7 @@
         </is>
       </c>
       <c r="F4" s="30" t="n">
-        <v>4187.1</v>
+        <v>4140.7</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="29">
@@ -5496,7 +5816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5978,9 +6298,53 @@
         </is>
       </c>
       <c r="K11" s="43" t="n">
-        <v>46302.58533634283</v>
+        <v>46302.58533634259</v>
       </c>
       <c r="L11" t="inlineStr">
+        <is>
+          <t>DEC 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="35" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>E21 Week 2 - OCT 2026 (V26)</t>
+        </is>
+      </c>
+      <c r="C12" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="42" t="n">
+        <v>4140.7</v>
+      </c>
+      <c r="E12" s="36" t="n">
+        <v>4190</v>
+      </c>
+      <c r="F12" s="38" t="n">
+        <v>0.01190619943487821</v>
+      </c>
+      <c r="G12" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" s="39" t="n">
+        <v>0.8681743788126767</v>
+      </c>
+      <c r="I12" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>FINAL</t>
+        </is>
+      </c>
+      <c r="K12" s="43" t="n">
+        <v>46304.43033637766</v>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>DEC 26</t>
         </is>
